--- a/data/trans_orig/P15B_tráfico-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15B_tráfico-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23493</t>
+          <t>23594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33717</t>
+          <t>33986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>31475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27050</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41796</t>
+          <t>41440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58951</t>
+          <t>58123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20879</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22074</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27041</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>40025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>22403</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>29132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21778</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35953</t>
+          <t>34996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48981</t>
+          <t>48899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>28731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46470</t>
+          <t>47830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>75745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70580</t>
+          <t>72517</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93001</t>
+          <t>93620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65804</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>81071</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143456</t>
+          <t>141138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170413</t>
+          <t>169053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>40079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52530</t>
+          <t>52686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>39694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50525</t>
+          <t>50315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>85020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100748</t>
+          <t>101021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27608</t>
+          <t>28959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20474</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43858</t>
+          <t>44033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53681</t>
+          <t>52330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68909</t>
+          <t>69443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54149</t>
+          <t>53362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67513</t>
+          <t>66611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112055</t>
+          <t>111880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>133040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>24690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21028</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>41486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34054</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47853</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36017</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48951</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73586</t>
+          <t>73967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92861</t>
+          <t>92554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>23414</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28911</t>
+          <t>28693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>52938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54105</t>
+          <t>54966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72163</t>
+          <t>71544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47990</t>
+          <t>47847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62743</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107139</t>
+          <t>106576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130603</t>
+          <t>130821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59210</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89346</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35916</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61910</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102019</t>
+          <t>103161</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141291</t>
+          <t>144262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197626</t>
+          <t>197917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227762</t>
+          <t>229550</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>193988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219489</t>
+          <t>219925</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401086</t>
+          <t>398115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>440358</t>
+          <t>439216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25252</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36023</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43986</t>
+          <t>43752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63166</t>
+          <t>63026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77264</t>
+          <t>77768</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40807</t>
+          <t>40345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54307</t>
+          <t>53971</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>33277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44612</t>
+          <t>44540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78141</t>
+          <t>78798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95965</t>
+          <t>96334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20810</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33620</t>
+          <t>33579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29570</t>
+          <t>29639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60990</t>
+          <t>61694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>23547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16651</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34546</t>
+          <t>35320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38086</t>
+          <t>37339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51161</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45967</t>
+          <t>45339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58296</t>
+          <t>57994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88958</t>
+          <t>88184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106751</t>
+          <t>106528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31443</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54840</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44404</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>61994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92239</t>
+          <t>91738</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142929</t>
+          <t>141268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166326</t>
+          <t>166166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147049</t>
+          <t>147234</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167875</t>
+          <t>168338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296984</t>
+          <t>297485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328808</t>
+          <t>327229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,07%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>20385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41491</t>
+          <t>44933</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36741</t>
+          <t>38613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43902</t>
+          <t>47755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35711</t>
+          <t>38702</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30545</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>42538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>77203</t>
+          <t>83634</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71093</t>
+          <t>76227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81838</t>
+          <t>88845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32760</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25830</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35895</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24535</t>
+          <t>26398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50305</t>
+          <t>52957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>45540</t>
+          <t>52578</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>40514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>61984</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41929</t>
+          <t>45884</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31405</t>
+          <t>35054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48982</t>
+          <t>53537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>87469</t>
+          <t>98461</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73059</t>
+          <t>83549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98829</t>
+          <t>110108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>73702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>136506</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>136506</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>136506</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>21999</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21254</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>29161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38929</t>
+          <t>43710</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31665</t>
+          <t>36367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>68352</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82452</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29485</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>20113</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>45259</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>35138</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50699</t>
+          <t>56578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>29892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44471</t>
+          <t>46008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50061</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55459</t>
+          <t>58946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>87678</t>
+          <t>91261</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77204</t>
+          <t>79942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96776</t>
+          <t>101382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>46168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70825</t>
+          <t>76711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60207</t>
+          <t>66540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>110382</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81571</t>
+          <t>90501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121571</t>
+          <t>131372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>145904</t>
+          <t>160554</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128305</t>
+          <t>143200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159605</t>
+          <t>173743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>166630</t>
+          <t>181155</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153396</t>
+          <t>165640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177633</t>
+          <t>193420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>312534</t>
+          <t>341709</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>291162</t>
+          <t>320719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>331162</t>
+          <t>361590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
